--- a/6 STATE STREAM 1 FOOD FOR HEALTH 18-10-2025 RANKLIST.xlsx
+++ b/6 STATE STREAM 1 FOOD FOR HEALTH 18-10-2025 RANKLIST.xlsx
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>93.33%</t>
+          <t>91.67%</t>
         </is>
       </c>
     </row>
@@ -902,11 +902,11 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>93.33%</t>
+          <t>91.67%</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1037,11 +1037,11 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -1082,11 +1082,11 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>83.33%</t>
         </is>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>83.33%</t>
         </is>
       </c>
     </row>
@@ -1172,11 +1172,11 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>83.33%</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1217,11 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>83.33%</t>
         </is>
       </c>
     </row>
@@ -1262,11 +1262,11 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.67%</t>
         </is>
       </c>
     </row>
@@ -1307,11 +1307,11 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.67%</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.67%</t>
         </is>
       </c>
     </row>
@@ -1397,11 +1397,11 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1442,11 +1442,11 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -1577,11 +1577,11 @@
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -1622,11 +1622,11 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>68.33%</t>
         </is>
       </c>
     </row>
@@ -1667,11 +1667,11 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>68.33%</t>
         </is>
       </c>
     </row>
@@ -1712,11 +1712,11 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -1757,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -1802,11 +1802,11 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -1847,11 +1847,11 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1892,11 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>73.33%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -1937,11 +1937,11 @@
         <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>61.67%</t>
         </is>
       </c>
     </row>
@@ -1982,11 +1982,11 @@
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2027,11 +2027,11 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2072,11 +2072,11 @@
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2117,11 +2117,11 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2162,11 +2162,11 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>58.33%</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2207,11 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>58.33%</t>
         </is>
       </c>
     </row>
@@ -2252,11 +2252,11 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>58.33%</t>
         </is>
       </c>
     </row>
@@ -2297,11 +2297,11 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>58.33%</t>
         </is>
       </c>
     </row>
@@ -2342,11 +2342,11 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2387,11 +2387,11 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2432,11 +2432,11 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2477,11 +2477,11 @@
         <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>46.67%</t>
         </is>
       </c>
     </row>
@@ -2522,11 +2522,11 @@
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>46.67%</t>
         </is>
       </c>
     </row>
@@ -2544,34 +2544,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F25061535</t>
+          <t>F25062519</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6S3</t>
+          <t>6S4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niya Nidheesh </t>
+          <t xml:space="preserve">Nidha Sarah Nabeel </t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>F25060739</t>
+          <t>F25061535</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manha Fathima </t>
+          <t xml:space="preserve">Niya Nidheesh </t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>F25062084</t>
+          <t>F25060739</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vamil Sagar </t>
+          <t xml:space="preserve">Manha Fathima </t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2657,11 +2657,11 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>43.33%</t>
         </is>
       </c>
     </row>
@@ -2679,17 +2679,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>F25060520</t>
+          <t>F25062084</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6S2</t>
+          <t>6S3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aradhya KP </t>
+          <t xml:space="preserve">Vamil Sagar </t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2702,11 +2702,11 @@
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>43.33%</t>
         </is>
       </c>
     </row>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F25062290</t>
+          <t>F25060520</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6S3</t>
+          <t>6S2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ishan ET </t>
+          <t xml:space="preserve">Aradhya KP </t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2747,11 +2747,11 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>43.33%</t>
         </is>
       </c>
     </row>
@@ -2769,34 +2769,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>F25060240</t>
+          <t>F25062290</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6S2</t>
+          <t>6S3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muhammed Shazil Manat </t>
+          <t xml:space="preserve">Ishan ET </t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>8</v>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>43.33%</t>
         </is>
       </c>
     </row>
@@ -2814,34 +2814,34 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>F25060956</t>
+          <t>F25060855</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6S3</t>
+          <t>6S1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rumaisa Sabeer </t>
+          <t xml:space="preserve">MUHAMMAD FIROS V </t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -2859,17 +2859,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>F25060795</t>
+          <t>F25060240</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6S1</t>
+          <t>6S2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aleena Falah K</t>
+          <t xml:space="preserve">Muhammed Shazil Manat </t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2882,11 +2882,11 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -2904,17 +2904,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>F25061878</t>
+          <t>F25060956</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6S1</t>
+          <t>6S3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thanza Fathima KM </t>
+          <t xml:space="preserve">Rumaisa Sabeer </t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2927,11 +2927,11 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -2949,17 +2949,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>F25061509</t>
+          <t>F25060795</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6S3</t>
+          <t>6S1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Afiya Anas </t>
+          <t>Aleena Falah K</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2972,11 +2972,11 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -2994,34 +2994,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>F25062519</t>
+          <t>F25061878</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6S4</t>
+          <t>6S1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nidha Sarah Nabeel </t>
+          <t xml:space="preserve">Thanza Fathima KM </t>
         </is>
       </c>
       <c r="G56" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" t="n">
         <v>7</v>
       </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -3039,34 +3039,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F25060855</t>
+          <t>F25061509</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6S1</t>
+          <t>6S3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUHAMMAD FIROS V </t>
+          <t xml:space="preserve">Afiya Anas </t>
         </is>
       </c>
       <c r="G57" t="n">
+        <v>8</v>
+      </c>
+      <c r="H57" t="n">
         <v>7</v>
       </c>
-      <c r="H57" t="n">
-        <v>3</v>
-      </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -3107,11 +3107,11 @@
         <v>3</v>
       </c>
       <c r="J58" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>38.33%</t>
         </is>
       </c>
     </row>
@@ -3152,11 +3152,11 @@
         <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>36.67%</t>
         </is>
       </c>
     </row>
@@ -3197,11 +3197,11 @@
         <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>36.67%</t>
         </is>
       </c>
     </row>
@@ -3242,11 +3242,11 @@
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>35.0%</t>
         </is>
       </c>
     </row>
@@ -3287,11 +3287,11 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
@@ -3332,11 +3332,11 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
@@ -3377,11 +3377,11 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
@@ -3422,11 +3422,11 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
@@ -3467,11 +3467,11 @@
         <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.67%</t>
         </is>
       </c>
     </row>
@@ -3512,11 +3512,11 @@
         <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.33%</t>
         </is>
       </c>
     </row>
@@ -3557,11 +3557,11 @@
         <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.67%</t>
         </is>
       </c>
     </row>
@@ -3602,11 +3602,11 @@
         <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.67%</t>
         </is>
       </c>
     </row>
@@ -3647,11 +3647,11 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3692,11 +3692,11 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3737,11 +3737,11 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3782,11 +3782,11 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3827,11 +3827,11 @@
         <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>18.33%</t>
         </is>
       </c>
     </row>
@@ -3872,11 +3872,11 @@
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>18.33%</t>
         </is>
       </c>
     </row>
@@ -3917,11 +3917,11 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -3962,11 +3962,11 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>26.67%</t>
+          <t>8.33%</t>
         </is>
       </c>
     </row>
